--- a/data_sources/master_data.xlsx
+++ b/data_sources/master_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Muham\Documents\ESMS-Code\mdr_app\data_sources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B78412-D910-48B9-A069-8442C21B8582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671BEB34-08C8-40C8-8893-094AC8EBBB92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="3" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,9 @@
     <sheet name="Disciplines" sheetId="7" r:id="rId7"/>
     <sheet name="Packages" sheetId="8" r:id="rId8"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">Packages!$A$1:$D$1</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -40,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2177" uniqueCount="1184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2180" uniqueCount="1186">
   <si>
     <t>code</t>
   </si>
@@ -3592,6 +3595,12 @@
   </si>
   <si>
     <t>48</t>
+  </si>
+  <si>
+    <t>پلان مرجع کدگذاری</t>
+  </si>
+  <si>
+    <t>Coding Reerence Plan</t>
   </si>
 </sst>
 </file>
@@ -5341,10 +5350,11 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:D468"/>
+  <dimension ref="A1:D469"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.6640625" style="6" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37.109375" bestFit="1" customWidth="1"/>
   </cols>
@@ -11901,7 +11911,22 @@
         <v>1012</v>
       </c>
     </row>
+    <row r="469" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A469" t="s">
+        <v>102</v>
+      </c>
+      <c r="B469" s="6">
+        <v>28</v>
+      </c>
+      <c r="C469" t="s">
+        <v>1185</v>
+      </c>
+      <c r="D469" t="s">
+        <v>1184</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:D1" xr:uid="{00000000-0001-0000-0700-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
     <ignoredError sqref="B2:B468" numberStoredAsText="1"/>
